--- a/Bizagi/simulation_parameters_alt.xlsx
+++ b/Bizagi/simulation_parameters_alt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28605"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mclau\source\repos\bizagi_simulations\Bizagi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{8FEF90F3-5287-4D36-B9DB-1E13D11FE41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C42FCDF-0097-42B5-BCDF-0E00035793D4}"/>
+  <xr:revisionPtr revIDLastSave="150" documentId="13_ncr:1_{8FEF90F3-5287-4D36-B9DB-1E13D11FE41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5D06352-8333-4D10-ACE6-D15F8A785F46}"/>
   <bookViews>
-    <workbookView xWindow="4485" yWindow="4530" windowWidth="25815" windowHeight="12030" firstSheet="3" activeTab="6" xr2:uid="{BB40CB68-33AA-4C15-B98B-3F539464DFB8}"/>
+    <workbookView xWindow="4485" yWindow="4530" windowWidth="25815" windowHeight="12030" firstSheet="6" xr2:uid="{BB40CB68-33AA-4C15-B98B-3F539464DFB8}"/>
   </bookViews>
   <sheets>
     <sheet name="ArrivalRate" sheetId="4" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
   <si>
     <t>Number Of Tokens</t>
   </si>
@@ -65,10 +65,28 @@
     <t>End Date</t>
   </si>
   <si>
-    <t>Start Time</t>
-  </si>
-  <si>
-    <t>End Time</t>
+    <t>Weekday Start</t>
+  </si>
+  <si>
+    <t>Weekday End</t>
+  </si>
+  <si>
+    <t>Saturday Start</t>
+  </si>
+  <si>
+    <t>Satuday End</t>
+  </si>
+  <si>
+    <t>Sunday Start</t>
+  </si>
+  <si>
+    <t>Sunday End</t>
+  </si>
+  <si>
+    <t>workday1</t>
+  </si>
+  <si>
+    <t>06/31/2025</t>
   </si>
   <si>
     <t>Resource Type</t>
@@ -77,6 +95,12 @@
     <t>Count</t>
   </si>
   <si>
+    <t>Technician</t>
+  </si>
+  <si>
+    <t>Certifier</t>
+  </si>
+  <si>
     <t>Activity</t>
   </si>
   <si>
@@ -89,6 +113,18 @@
     <t>Maximum Time</t>
   </si>
   <si>
+    <t>Review AM Using Asset Change Tracker (5.5.13.1)</t>
+  </si>
+  <si>
+    <t>Note Accuracy in Asset Change Tracker (5.5.13.2)</t>
+  </si>
+  <si>
+    <t>Work with REO RPO to Correct (5.5.13.3)</t>
+  </si>
+  <si>
+    <t>Create/Post Journal Entries (5.5.13.4)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Resource Type    </t>
   </si>
   <si>
@@ -101,14 +137,23 @@
     <t>Gateway</t>
   </si>
   <si>
-    <t>Probability</t>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Complete /Accurate?</t>
+  </si>
+  <si>
+    <t>Create Journal Entries?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,6 +176,19 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -152,11 +210,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -491,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4600DEE3-02C0-426B-B894-AA57D064E870}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -514,6 +575,20 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>1000</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -521,16 +596,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8027725D-026D-4DCB-BF14-24A5DC527760}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -545,6 +625,35 @@
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="4">
+        <v>45658</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2">
+        <v>600</v>
+      </c>
+      <c r="E2">
+        <v>1300</v>
       </c>
     </row>
   </sheetData>
@@ -554,7 +663,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29524C21-B913-47CF-B5D6-9B2F7FC8B42A}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
@@ -562,10 +671,26 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17.25">
       <c r="A1" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -575,7 +700,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2C56BC4-0F72-4B03-847B-592B0454C405}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -587,10 +712,32 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -600,9 +747,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE379637-95A8-4067-BF2B-B4758181AE3D}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="75.140625" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
@@ -610,16 +758,72 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25">
       <c r="A1" s="2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>8</v>
+      </c>
+      <c r="D2">
         <v>12</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>14</v>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4">
+        <v>60</v>
+      </c>
+      <c r="C4">
+        <v>120</v>
+      </c>
+      <c r="D4">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -629,28 +833,71 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B02B12B8-C73F-4B04-8F28-5AFC9C447DA8}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="57" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2" s="3"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -659,19 +906,44 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A50A12-B451-4803-A175-62686732A685}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.140625" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="17.25">
+    <row r="1" spans="1:3" ht="17.25">
       <c r="A1" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="C1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="C2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3">
+        <v>0.5</v>
+      </c>
+      <c r="C3">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
